--- a/VerveStacks_USA/vt_vervestacks_USA_v1.xlsx
+++ b/VerveStacks_USA/vt_vervestacks_USA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_USA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C5DD8386-2BD8-47E7-A6AB-D53AD612307A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7FD3F757-D6C5-4EE5-9325-019582F55AAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{37A029BF-1F60-4969-9A84-1A50C192EDB6}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{1154C19B-1B8D-4834-8B4C-E55DA0EDD142}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -5507,7 +5507,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74B6D0A5-A4FF-49B7-8408-461DDE78992D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE5C5268-BDB2-4314-9819-325CDDB564F6}">
   <dimension ref="B9:T503"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -25986,7 +25986,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79D8FEEF-9B47-477A-ADC2-3A06AFD5ABAB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93A909F4-0DDD-45CD-8D8F-C1D65B016CB9}">
   <dimension ref="B9:T1313"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -70874,7 +70874,7 @@
         <v>33</v>
       </c>
       <c r="L949">
-        <v>0.24073684438920245</v>
+        <v>0.24073684438920243</v>
       </c>
     </row>
     <row r="950" spans="2:12" x14ac:dyDescent="0.45">

--- a/VerveStacks_USA/vt_vervestacks_USA_v1.xlsx
+++ b/VerveStacks_USA/vt_vervestacks_USA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_USA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7FD3F757-D6C5-4EE5-9325-019582F55AAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5224FC50-650E-4AEF-A6B0-1C4D127D51B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{1154C19B-1B8D-4834-8B4C-E55DA0EDD142}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{35453DD7-59B6-446D-B5AE-79D0D88E4710}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -5507,7 +5507,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE5C5268-BDB2-4314-9819-325CDDB564F6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D00C87AA-A0AC-4425-8C46-8D7C4761428C}">
   <dimension ref="B9:T503"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -25986,7 +25986,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93A909F4-0DDD-45CD-8D8F-C1D65B016CB9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D1DD037-28A7-411B-A812-CFC232B22D21}">
   <dimension ref="B9:T1313"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -70874,7 +70874,7 @@
         <v>33</v>
       </c>
       <c r="L949">
-        <v>0.24073684438920243</v>
+        <v>0.24073684438920245</v>
       </c>
     </row>
     <row r="950" spans="2:12" x14ac:dyDescent="0.45">

--- a/VerveStacks_USA/vt_vervestacks_USA_v1.xlsx
+++ b/VerveStacks_USA/vt_vervestacks_USA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_USA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5224FC50-650E-4AEF-A6B0-1C4D127D51B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{347DCEB7-99ED-43C4-A364-57DBBE697FFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{35453DD7-59B6-446D-B5AE-79D0D88E4710}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{A0A898E9-0FC9-4704-AB33-296B0D62FBC4}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -5507,7 +5507,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D00C87AA-A0AC-4425-8C46-8D7C4761428C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED347244-461C-4AAD-B314-FFF083BC5DA2}">
   <dimension ref="B9:T503"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -25986,7 +25986,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D1DD037-28A7-411B-A812-CFC232B22D21}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CFCBCF6-AFCE-4AA1-8B3F-B131CFA41337}">
   <dimension ref="B9:T1313"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_USA/vt_vervestacks_USA_v1.xlsx
+++ b/VerveStacks_USA/vt_vervestacks_USA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_USA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{347DCEB7-99ED-43C4-A364-57DBBE697FFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DDCDB2D1-24E8-4FBF-B220-09C8AB8748BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{A0A898E9-0FC9-4704-AB33-296B0D62FBC4}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{AC844C9F-9C4E-4390-88D9-C1CCA4A1E980}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -5507,7 +5507,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED347244-461C-4AAD-B314-FFF083BC5DA2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCB02EA1-D29B-4861-8E06-84E477CD2493}">
   <dimension ref="B9:T503"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -25986,7 +25986,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CFCBCF6-AFCE-4AA1-8B3F-B131CFA41337}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF03285B-1BB6-40B3-8C35-54A7DB359CC6}">
   <dimension ref="B9:T1313"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -70874,7 +70874,7 @@
         <v>33</v>
       </c>
       <c r="L949">
-        <v>0.24073684438920245</v>
+        <v>0.24073684438920243</v>
       </c>
     </row>
     <row r="950" spans="2:12" x14ac:dyDescent="0.45">

--- a/VerveStacks_USA/vt_vervestacks_USA_v1.xlsx
+++ b/VerveStacks_USA/vt_vervestacks_USA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_USA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DDCDB2D1-24E8-4FBF-B220-09C8AB8748BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{72492431-F490-4CB0-A29D-315061297F76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{AC844C9F-9C4E-4390-88D9-C1CCA4A1E980}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{C637B9A5-15C2-45C5-ADFB-3B26A38C1B00}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -5507,7 +5507,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCB02EA1-D29B-4861-8E06-84E477CD2493}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA049857-744B-49E9-82C6-FF76621036DC}">
   <dimension ref="B9:T503"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -25986,7 +25986,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF03285B-1BB6-40B3-8C35-54A7DB359CC6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{330F6A3B-447D-4749-AE29-1EE7D8F31F23}">
   <dimension ref="B9:T1313"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -70874,7 +70874,7 @@
         <v>33</v>
       </c>
       <c r="L949">
-        <v>0.24073684438920243</v>
+        <v>0.24073684438920245</v>
       </c>
     </row>
     <row r="950" spans="2:12" x14ac:dyDescent="0.45">

--- a/VerveStacks_USA/vt_vervestacks_USA_v1.xlsx
+++ b/VerveStacks_USA/vt_vervestacks_USA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_USA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{72492431-F490-4CB0-A29D-315061297F76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C3B96C76-13F4-40DE-BB5F-A0736CD12CA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{C637B9A5-15C2-45C5-ADFB-3B26A38C1B00}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{94D7EDDB-4050-4319-849E-F4ABE69392EA}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -5507,7 +5507,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA049857-744B-49E9-82C6-FF76621036DC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6426940B-5190-4A63-B348-0D36BB2246EE}">
   <dimension ref="B9:T503"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -25986,7 +25986,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{330F6A3B-447D-4749-AE29-1EE7D8F31F23}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D04CDF2F-C866-48BE-8011-A12F25D410B0}">
   <dimension ref="B9:T1313"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_USA/vt_vervestacks_USA_v1.xlsx
+++ b/VerveStacks_USA/vt_vervestacks_USA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_USA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C3B96C76-13F4-40DE-BB5F-A0736CD12CA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B42F7927-9465-4735-BE0F-4582ACBE8B35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{94D7EDDB-4050-4319-849E-F4ABE69392EA}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{03B880F7-6AB4-4093-B565-A944A55A3FB1}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -5507,7 +5507,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6426940B-5190-4A63-B348-0D36BB2246EE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{957C2361-D968-4121-881C-2F65967D5DF7}">
   <dimension ref="B9:T503"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -5586,7 +5586,7 @@
         <v>14</v>
       </c>
       <c r="E11">
-        <v>0.11096000000000002</v>
+        <v>0.11206960000000001</v>
       </c>
       <c r="F11">
         <v>3583</v>
@@ -5642,7 +5642,7 @@
         <v>14</v>
       </c>
       <c r="E12">
-        <v>0.12410530764449972</v>
+        <v>0.12534636072094471</v>
       </c>
       <c r="F12">
         <v>3583</v>
@@ -5698,7 +5698,7 @@
         <v>14</v>
       </c>
       <c r="E13">
-        <v>8.5120000000000029E-2</v>
+        <v>8.5971200000000039E-2</v>
       </c>
       <c r="F13">
         <v>3583</v>
@@ -5754,19 +5754,19 @@
         <v>14</v>
       </c>
       <c r="E14">
-        <v>0.28050000000000003</v>
+        <v>0.29017300000000001</v>
       </c>
       <c r="F14">
-        <v>1923</v>
+        <v>1726</v>
       </c>
       <c r="G14">
-        <v>22.9</v>
+        <v>20.9</v>
       </c>
       <c r="H14">
-        <v>2.88</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="I14">
-        <v>0.80844999999999989</v>
+        <v>0.82269999999999999</v>
       </c>
       <c r="J14" t="s">
         <v>83</v>
@@ -5810,7 +5810,7 @@
         <v>14</v>
       </c>
       <c r="E15">
-        <v>0.29575000000000001</v>
+        <v>0.29870749999999996</v>
       </c>
       <c r="F15">
         <v>1726</v>
@@ -5866,7 +5866,7 @@
         <v>14</v>
       </c>
       <c r="E16">
-        <v>0.29575000000000001</v>
+        <v>0.29870749999999996</v>
       </c>
       <c r="F16">
         <v>1726</v>
@@ -5922,7 +5922,7 @@
         <v>14</v>
       </c>
       <c r="E17">
-        <v>0.30419999999999997</v>
+        <v>0.30724200000000002</v>
       </c>
       <c r="F17">
         <v>1726</v>
@@ -5978,7 +5978,7 @@
         <v>14</v>
       </c>
       <c r="E18">
-        <v>0.2957499999999999</v>
+        <v>0.29870749999999996</v>
       </c>
       <c r="F18">
         <v>1726</v>
@@ -6034,7 +6034,7 @@
         <v>14</v>
       </c>
       <c r="E19">
-        <v>0.29575000000000001</v>
+        <v>0.29870749999999996</v>
       </c>
       <c r="F19">
         <v>1726</v>
@@ -6090,19 +6090,19 @@
         <v>14</v>
       </c>
       <c r="E20">
-        <v>0.28050000000000003</v>
+        <v>0.29017300000000001</v>
       </c>
       <c r="F20">
-        <v>1923</v>
+        <v>1726</v>
       </c>
       <c r="G20">
-        <v>22.9</v>
+        <v>20.9</v>
       </c>
       <c r="H20">
-        <v>2.88</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="I20">
-        <v>0.80844999999999989</v>
+        <v>0.82269999999999999</v>
       </c>
       <c r="J20" t="s">
         <v>89</v>
@@ -6146,19 +6146,19 @@
         <v>14</v>
       </c>
       <c r="E21">
-        <v>0.28050000000000003</v>
+        <v>0.29017300000000001</v>
       </c>
       <c r="F21">
-        <v>1923</v>
+        <v>1726</v>
       </c>
       <c r="G21">
-        <v>22.9</v>
+        <v>20.9</v>
       </c>
       <c r="H21">
-        <v>2.88</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="I21">
-        <v>0.80844999999999989</v>
+        <v>0.82269999999999999</v>
       </c>
       <c r="J21" t="s">
         <v>90</v>
@@ -6202,7 +6202,7 @@
         <v>14</v>
       </c>
       <c r="E22">
-        <v>0.29575000000000001</v>
+        <v>0.29870749999999996</v>
       </c>
       <c r="F22">
         <v>1726</v>
@@ -6258,7 +6258,7 @@
         <v>14</v>
       </c>
       <c r="E23">
-        <v>0.29575000000000001</v>
+        <v>0.29870749999999996</v>
       </c>
       <c r="F23">
         <v>1726</v>
@@ -6314,7 +6314,7 @@
         <v>14</v>
       </c>
       <c r="E24">
-        <v>0.29575000000000001</v>
+        <v>0.29870749999999996</v>
       </c>
       <c r="F24">
         <v>1726</v>
@@ -6370,7 +6370,7 @@
         <v>14</v>
       </c>
       <c r="E25">
-        <v>0.29575000000000001</v>
+        <v>0.29870749999999996</v>
       </c>
       <c r="F25">
         <v>1726</v>
@@ -6426,19 +6426,19 @@
         <v>14</v>
       </c>
       <c r="E26">
-        <v>0.28050000000000003</v>
+        <v>0.29017300000000001</v>
       </c>
       <c r="F26">
-        <v>1923</v>
+        <v>1726</v>
       </c>
       <c r="G26">
-        <v>22.9</v>
+        <v>20.9</v>
       </c>
       <c r="H26">
-        <v>2.88</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="I26">
-        <v>0.80844999999999989</v>
+        <v>0.82269999999999999</v>
       </c>
       <c r="J26" t="s">
         <v>95</v>
@@ -6482,7 +6482,7 @@
         <v>14</v>
       </c>
       <c r="E27">
-        <v>0.29575000000000001</v>
+        <v>0.29870749999999996</v>
       </c>
       <c r="F27">
         <v>1726</v>
@@ -6538,7 +6538,7 @@
         <v>14</v>
       </c>
       <c r="E28">
-        <v>0.10944000000000001</v>
+        <v>0.11053440000000002</v>
       </c>
       <c r="F28">
         <v>3583</v>
@@ -6594,7 +6594,7 @@
         <v>14</v>
       </c>
       <c r="E29">
-        <v>0.10944000000000001</v>
+        <v>0.11053440000000002</v>
       </c>
       <c r="F29">
         <v>3583</v>
@@ -6650,7 +6650,7 @@
         <v>14</v>
       </c>
       <c r="E30">
-        <v>0.10944000000000001</v>
+        <v>0.11053440000000002</v>
       </c>
       <c r="F30">
         <v>3583</v>
@@ -6706,7 +6706,7 @@
         <v>14</v>
       </c>
       <c r="E31">
-        <v>0.10944000000000001</v>
+        <v>0.11053440000000002</v>
       </c>
       <c r="F31">
         <v>3583</v>
@@ -6762,7 +6762,7 @@
         <v>14</v>
       </c>
       <c r="E32">
-        <v>0.10944000000000001</v>
+        <v>0.11053440000000002</v>
       </c>
       <c r="F32">
         <v>3583</v>
@@ -6818,7 +6818,7 @@
         <v>14</v>
       </c>
       <c r="E33">
-        <v>0.10944000000000001</v>
+        <v>0.11053440000000002</v>
       </c>
       <c r="F33">
         <v>3583</v>
@@ -6874,7 +6874,7 @@
         <v>14</v>
       </c>
       <c r="E34">
-        <v>0.10944000000000001</v>
+        <v>0.11053440000000002</v>
       </c>
       <c r="F34">
         <v>3583</v>
@@ -6930,7 +6930,7 @@
         <v>14</v>
       </c>
       <c r="E35">
-        <v>0.10944000000000001</v>
+        <v>0.11053440000000002</v>
       </c>
       <c r="F35">
         <v>3583</v>
@@ -6986,7 +6986,7 @@
         <v>14</v>
       </c>
       <c r="E36">
-        <v>0.10944000000000001</v>
+        <v>0.11053440000000002</v>
       </c>
       <c r="F36">
         <v>3583</v>
@@ -7042,7 +7042,7 @@
         <v>14</v>
       </c>
       <c r="E37">
-        <v>0.10944000000000001</v>
+        <v>0.11053440000000002</v>
       </c>
       <c r="F37">
         <v>3583</v>
@@ -7098,7 +7098,7 @@
         <v>14</v>
       </c>
       <c r="E38">
-        <v>0.10944000000000001</v>
+        <v>0.11053440000000002</v>
       </c>
       <c r="F38">
         <v>3583</v>
@@ -7154,7 +7154,7 @@
         <v>14</v>
       </c>
       <c r="E39">
-        <v>0.10944000000000001</v>
+        <v>0.11053440000000002</v>
       </c>
       <c r="F39">
         <v>3583</v>
@@ -7210,7 +7210,7 @@
         <v>14</v>
       </c>
       <c r="E40">
-        <v>0.10944000000000001</v>
+        <v>0.11053440000000002</v>
       </c>
       <c r="F40">
         <v>3583</v>
@@ -7266,7 +7266,7 @@
         <v>14</v>
       </c>
       <c r="E41">
-        <v>0.10944000000000001</v>
+        <v>0.11053440000000002</v>
       </c>
       <c r="F41">
         <v>3583</v>
@@ -7322,7 +7322,7 @@
         <v>14</v>
       </c>
       <c r="E42">
-        <v>0.10944000000000001</v>
+        <v>0.11053440000000002</v>
       </c>
       <c r="F42">
         <v>3583</v>
@@ -7378,7 +7378,7 @@
         <v>14</v>
       </c>
       <c r="E43">
-        <v>0.10944000000000001</v>
+        <v>0.11053440000000002</v>
       </c>
       <c r="F43">
         <v>3583</v>
@@ -7434,7 +7434,7 @@
         <v>14</v>
       </c>
       <c r="E44">
-        <v>0.10944000000000001</v>
+        <v>0.11053440000000002</v>
       </c>
       <c r="F44">
         <v>3583</v>
@@ -7490,7 +7490,7 @@
         <v>14</v>
       </c>
       <c r="E45">
-        <v>0.10944000000000001</v>
+        <v>0.11053440000000002</v>
       </c>
       <c r="F45">
         <v>3583</v>
@@ -7546,7 +7546,7 @@
         <v>14</v>
       </c>
       <c r="E46">
-        <v>0.10944000000000001</v>
+        <v>0.11053440000000002</v>
       </c>
       <c r="F46">
         <v>3583</v>
@@ -7602,7 +7602,7 @@
         <v>14</v>
       </c>
       <c r="E47">
-        <v>0.10944000000000001</v>
+        <v>0.11053440000000002</v>
       </c>
       <c r="F47">
         <v>3583</v>
@@ -7658,7 +7658,7 @@
         <v>14</v>
       </c>
       <c r="E48">
-        <v>0.10944000000000001</v>
+        <v>0.11053440000000002</v>
       </c>
       <c r="F48">
         <v>3583</v>
@@ -7714,7 +7714,7 @@
         <v>14</v>
       </c>
       <c r="E49">
-        <v>0.10944000000000001</v>
+        <v>0.11053440000000002</v>
       </c>
       <c r="F49">
         <v>3583</v>
@@ -7770,7 +7770,7 @@
         <v>14</v>
       </c>
       <c r="E50">
-        <v>0.10944000000000001</v>
+        <v>0.11053440000000002</v>
       </c>
       <c r="F50">
         <v>3583</v>
@@ -7826,7 +7826,7 @@
         <v>14</v>
       </c>
       <c r="E51">
-        <v>0.10944000000000001</v>
+        <v>0.11053440000000002</v>
       </c>
       <c r="F51">
         <v>3583</v>
@@ -7882,7 +7882,7 @@
         <v>14</v>
       </c>
       <c r="E52">
-        <v>0.10944000000000001</v>
+        <v>0.11053440000000002</v>
       </c>
       <c r="F52">
         <v>3583</v>
@@ -7938,7 +7938,7 @@
         <v>14</v>
       </c>
       <c r="E53">
-        <v>0.10944000000000001</v>
+        <v>0.11053440000000002</v>
       </c>
       <c r="F53">
         <v>3583</v>
@@ -7994,7 +7994,7 @@
         <v>14</v>
       </c>
       <c r="E54">
-        <v>0.10944000000000001</v>
+        <v>0.11053440000000002</v>
       </c>
       <c r="F54">
         <v>3583</v>
@@ -8050,7 +8050,7 @@
         <v>14</v>
       </c>
       <c r="E55">
-        <v>0.10944000000000001</v>
+        <v>0.11053440000000002</v>
       </c>
       <c r="F55">
         <v>3583</v>
@@ -8106,7 +8106,7 @@
         <v>14</v>
       </c>
       <c r="E56">
-        <v>0.10944000000000001</v>
+        <v>0.11053440000000002</v>
       </c>
       <c r="F56">
         <v>3583</v>
@@ -8162,7 +8162,7 @@
         <v>14</v>
       </c>
       <c r="E57">
-        <v>0.10944000000000001</v>
+        <v>0.11053440000000002</v>
       </c>
       <c r="F57">
         <v>3583</v>
@@ -8218,7 +8218,7 @@
         <v>14</v>
       </c>
       <c r="E58">
-        <v>0.10944000000000001</v>
+        <v>0.11053440000000002</v>
       </c>
       <c r="F58">
         <v>3583</v>
@@ -8274,7 +8274,7 @@
         <v>14</v>
       </c>
       <c r="E59">
-        <v>0.10944000000000001</v>
+        <v>0.11053440000000002</v>
       </c>
       <c r="F59">
         <v>3583</v>
@@ -8330,7 +8330,7 @@
         <v>14</v>
       </c>
       <c r="E60">
-        <v>0.10944000000000001</v>
+        <v>0.11053440000000002</v>
       </c>
       <c r="F60">
         <v>3583</v>
@@ -8386,7 +8386,7 @@
         <v>14</v>
       </c>
       <c r="E61">
-        <v>0.10944000000000001</v>
+        <v>0.11053440000000002</v>
       </c>
       <c r="F61">
         <v>3583</v>
@@ -8442,7 +8442,7 @@
         <v>14</v>
       </c>
       <c r="E62">
-        <v>0.10944000000000001</v>
+        <v>0.11053440000000002</v>
       </c>
       <c r="F62">
         <v>3583</v>
@@ -8498,7 +8498,7 @@
         <v>14</v>
       </c>
       <c r="E63">
-        <v>0.10944000000000001</v>
+        <v>0.11053440000000002</v>
       </c>
       <c r="F63">
         <v>3583</v>
@@ -8554,7 +8554,7 @@
         <v>14</v>
       </c>
       <c r="E64">
-        <v>0.10944000000000001</v>
+        <v>0.11053440000000002</v>
       </c>
       <c r="F64">
         <v>3583</v>
@@ -8610,7 +8610,7 @@
         <v>14</v>
       </c>
       <c r="E65">
-        <v>0.10944000000000001</v>
+        <v>0.11053440000000002</v>
       </c>
       <c r="F65">
         <v>3583</v>
@@ -8666,7 +8666,7 @@
         <v>14</v>
       </c>
       <c r="E66">
-        <v>0.10944000000000001</v>
+        <v>0.11053440000000002</v>
       </c>
       <c r="F66">
         <v>3583</v>
@@ -8722,7 +8722,7 @@
         <v>14</v>
       </c>
       <c r="E67">
-        <v>0.10944000000000001</v>
+        <v>0.11053440000000002</v>
       </c>
       <c r="F67">
         <v>3583</v>
@@ -8778,7 +8778,7 @@
         <v>14</v>
       </c>
       <c r="E68">
-        <v>0.10944000000000001</v>
+        <v>0.11053440000000002</v>
       </c>
       <c r="F68">
         <v>3583</v>
@@ -8834,7 +8834,7 @@
         <v>14</v>
       </c>
       <c r="E69">
-        <v>0.10944000000000001</v>
+        <v>0.11053440000000002</v>
       </c>
       <c r="F69">
         <v>3583</v>
@@ -8890,7 +8890,7 @@
         <v>14</v>
       </c>
       <c r="E70">
-        <v>0.10944000000000001</v>
+        <v>0.11053440000000002</v>
       </c>
       <c r="F70">
         <v>3583</v>
@@ -8946,7 +8946,7 @@
         <v>14</v>
       </c>
       <c r="E71">
-        <v>0.10944000000000001</v>
+        <v>0.11053440000000002</v>
       </c>
       <c r="F71">
         <v>3583</v>
@@ -9002,7 +9002,7 @@
         <v>14</v>
       </c>
       <c r="E72">
-        <v>0.10944000000000001</v>
+        <v>0.11053440000000002</v>
       </c>
       <c r="F72">
         <v>3583</v>
@@ -9058,7 +9058,7 @@
         <v>14</v>
       </c>
       <c r="E73">
-        <v>0.10944000000000001</v>
+        <v>0.11053440000000002</v>
       </c>
       <c r="F73">
         <v>3583</v>
@@ -9114,7 +9114,7 @@
         <v>14</v>
       </c>
       <c r="E74">
-        <v>0.10944000000000001</v>
+        <v>0.11053440000000002</v>
       </c>
       <c r="F74">
         <v>3583</v>
@@ -9170,7 +9170,7 @@
         <v>14</v>
       </c>
       <c r="E75">
-        <v>0.10944000000000001</v>
+        <v>0.11053440000000002</v>
       </c>
       <c r="F75">
         <v>3583</v>
@@ -9226,7 +9226,7 @@
         <v>14</v>
       </c>
       <c r="E76">
-        <v>0.10944000000000001</v>
+        <v>0.11053440000000002</v>
       </c>
       <c r="F76">
         <v>3583</v>
@@ -9282,7 +9282,7 @@
         <v>14</v>
       </c>
       <c r="E77">
-        <v>0.10944000000000001</v>
+        <v>0.11053440000000002</v>
       </c>
       <c r="F77">
         <v>3583</v>
@@ -9338,7 +9338,7 @@
         <v>14</v>
       </c>
       <c r="E78">
-        <v>0.10944000000000001</v>
+        <v>0.11053440000000002</v>
       </c>
       <c r="F78">
         <v>3583</v>
@@ -9394,7 +9394,7 @@
         <v>14</v>
       </c>
       <c r="E79">
-        <v>0.10944000000000001</v>
+        <v>0.11053440000000002</v>
       </c>
       <c r="F79">
         <v>3583</v>
@@ -9450,7 +9450,7 @@
         <v>14</v>
       </c>
       <c r="E80">
-        <v>0.10944000000000001</v>
+        <v>0.11053440000000002</v>
       </c>
       <c r="F80">
         <v>3583</v>
@@ -9506,7 +9506,7 @@
         <v>14</v>
       </c>
       <c r="E81">
-        <v>0.10944000000000001</v>
+        <v>0.11053440000000002</v>
       </c>
       <c r="F81">
         <v>3583</v>
@@ -9562,7 +9562,7 @@
         <v>14</v>
       </c>
       <c r="E82">
-        <v>0.10944000000000001</v>
+        <v>0.11053440000000002</v>
       </c>
       <c r="F82">
         <v>3583</v>
@@ -9618,7 +9618,7 @@
         <v>14</v>
       </c>
       <c r="E83">
-        <v>0.10944000000000001</v>
+        <v>0.11053440000000002</v>
       </c>
       <c r="F83">
         <v>3583</v>
@@ -9674,7 +9674,7 @@
         <v>14</v>
       </c>
       <c r="E84">
-        <v>0.10944000000000001</v>
+        <v>0.11053440000000002</v>
       </c>
       <c r="F84">
         <v>3583</v>
@@ -9730,7 +9730,7 @@
         <v>14</v>
       </c>
       <c r="E85">
-        <v>0.10944000000000001</v>
+        <v>0.11053440000000002</v>
       </c>
       <c r="F85">
         <v>3583</v>
@@ -9786,7 +9786,7 @@
         <v>14</v>
       </c>
       <c r="E86">
-        <v>0.10944000000000001</v>
+        <v>0.11053440000000002</v>
       </c>
       <c r="F86">
         <v>3583</v>
@@ -9842,7 +9842,7 @@
         <v>14</v>
       </c>
       <c r="E87">
-        <v>0.10944000000000001</v>
+        <v>0.11053440000000002</v>
       </c>
       <c r="F87">
         <v>3583</v>
@@ -9898,7 +9898,7 @@
         <v>14</v>
       </c>
       <c r="E88">
-        <v>0.10944000000000001</v>
+        <v>0.11053440000000002</v>
       </c>
       <c r="F88">
         <v>3583</v>
@@ -9954,19 +9954,19 @@
         <v>14</v>
       </c>
       <c r="E89">
-        <v>0.28050000000000003</v>
+        <v>0.29017300000000001</v>
       </c>
       <c r="F89">
-        <v>1923</v>
+        <v>1726</v>
       </c>
       <c r="G89">
-        <v>22.9</v>
+        <v>20.9</v>
       </c>
       <c r="H89">
-        <v>2.88</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="I89">
-        <v>0.80844999999999989</v>
+        <v>0.82269999999999999</v>
       </c>
       <c r="J89" t="s">
         <v>98</v>
@@ -10010,19 +10010,19 @@
         <v>14</v>
       </c>
       <c r="E90">
-        <v>0.28050000000000003</v>
+        <v>0.29017300000000001</v>
       </c>
       <c r="F90">
-        <v>1923</v>
+        <v>1726</v>
       </c>
       <c r="G90">
-        <v>22.9</v>
+        <v>20.9</v>
       </c>
       <c r="H90">
-        <v>2.88</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="I90">
-        <v>0.80844999999999989</v>
+        <v>0.82269999999999999</v>
       </c>
       <c r="J90" t="s">
         <v>99</v>
@@ -10066,19 +10066,19 @@
         <v>14</v>
       </c>
       <c r="E91">
-        <v>0.28050000000000003</v>
+        <v>0.29017300000000001</v>
       </c>
       <c r="F91">
-        <v>1923</v>
+        <v>1726</v>
       </c>
       <c r="G91">
-        <v>22.9</v>
+        <v>20.9</v>
       </c>
       <c r="H91">
-        <v>2.88</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="I91">
-        <v>0.80844999999999989</v>
+        <v>0.82269999999999999</v>
       </c>
       <c r="J91" t="s">
         <v>100</v>
@@ -10122,7 +10122,7 @@
         <v>14</v>
       </c>
       <c r="E92">
-        <v>0.26400000000000001</v>
+        <v>0.26663999999999999</v>
       </c>
       <c r="F92">
         <v>1923</v>
@@ -10178,19 +10178,19 @@
         <v>14</v>
       </c>
       <c r="E93">
-        <v>0.28050000000000003</v>
+        <v>0.29017300000000001</v>
       </c>
       <c r="F93">
-        <v>1923</v>
+        <v>1726</v>
       </c>
       <c r="G93">
-        <v>22.9</v>
+        <v>20.9</v>
       </c>
       <c r="H93">
-        <v>2.88</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="I93">
-        <v>0.80844999999999989</v>
+        <v>0.82269999999999999</v>
       </c>
       <c r="J93" t="s">
         <v>102</v>
@@ -10234,7 +10234,7 @@
         <v>14</v>
       </c>
       <c r="E94">
-        <v>0.33377499999999999</v>
+        <v>0.33711275000000002</v>
       </c>
       <c r="F94">
         <v>1726</v>
@@ -10290,19 +10290,19 @@
         <v>14</v>
       </c>
       <c r="E95">
-        <v>0.28050000000000003</v>
+        <v>0.29017300000000001</v>
       </c>
       <c r="F95">
-        <v>1923</v>
+        <v>1726</v>
       </c>
       <c r="G95">
-        <v>22.9</v>
+        <v>20.9</v>
       </c>
       <c r="H95">
-        <v>2.88</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="I95">
-        <v>0.80844999999999989</v>
+        <v>0.82269999999999999</v>
       </c>
       <c r="J95" t="s">
         <v>104</v>
@@ -10346,19 +10346,19 @@
         <v>14</v>
       </c>
       <c r="E96">
-        <v>0.28050000000000003</v>
+        <v>0.29017300000000001</v>
       </c>
       <c r="F96">
-        <v>1923</v>
+        <v>1726</v>
       </c>
       <c r="G96">
-        <v>22.9</v>
+        <v>20.9</v>
       </c>
       <c r="H96">
-        <v>2.88</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="I96">
-        <v>0.80844999999999989</v>
+        <v>0.82269999999999999</v>
       </c>
       <c r="J96" t="s">
         <v>105</v>
@@ -10402,19 +10402,19 @@
         <v>14</v>
       </c>
       <c r="E97">
-        <v>0.28050000000000003</v>
+        <v>0.29017300000000001</v>
       </c>
       <c r="F97">
-        <v>1923</v>
+        <v>1726</v>
       </c>
       <c r="G97">
-        <v>22.9</v>
+        <v>20.9</v>
       </c>
       <c r="H97">
-        <v>2.88</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="I97">
-        <v>0.80844999999999989</v>
+        <v>0.82269999999999999</v>
       </c>
       <c r="J97" t="s">
         <v>106</v>
@@ -10458,19 +10458,19 @@
         <v>14</v>
       </c>
       <c r="E98">
-        <v>0.28050000000000003</v>
+        <v>0.29017300000000001</v>
       </c>
       <c r="F98">
-        <v>1923</v>
+        <v>1726</v>
       </c>
       <c r="G98">
-        <v>22.9</v>
+        <v>20.9</v>
       </c>
       <c r="H98">
-        <v>2.88</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="I98">
-        <v>0.80844999999999989</v>
+        <v>0.82269999999999999</v>
       </c>
       <c r="J98" t="s">
         <v>107</v>
@@ -10514,19 +10514,19 @@
         <v>14</v>
       </c>
       <c r="E99">
-        <v>0.28050000000000003</v>
+        <v>0.29017300000000001</v>
       </c>
       <c r="F99">
-        <v>1923</v>
+        <v>1726</v>
       </c>
       <c r="G99">
-        <v>22.9</v>
+        <v>20.9</v>
       </c>
       <c r="H99">
-        <v>2.88</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="I99">
-        <v>0.80844999999999989</v>
+        <v>0.82269999999999999</v>
       </c>
       <c r="J99" t="s">
         <v>108</v>
@@ -10570,7 +10570,7 @@
         <v>14</v>
       </c>
       <c r="E100">
-        <v>0.33377500000000004</v>
+        <v>0.33711275000000002</v>
       </c>
       <c r="F100">
         <v>1726</v>
@@ -10626,7 +10626,7 @@
         <v>14</v>
       </c>
       <c r="E101">
-        <v>0.26400000000000001</v>
+        <v>0.26663999999999999</v>
       </c>
       <c r="F101">
         <v>1923</v>
@@ -10682,7 +10682,7 @@
         <v>14</v>
       </c>
       <c r="E102">
-        <v>0.26400000000000001</v>
+        <v>0.26663999999999999</v>
       </c>
       <c r="F102">
         <v>1923</v>
@@ -10738,19 +10738,19 @@
         <v>14</v>
       </c>
       <c r="E103">
-        <v>0.28050000000000003</v>
+        <v>0.29017300000000001</v>
       </c>
       <c r="F103">
-        <v>1923</v>
+        <v>1726</v>
       </c>
       <c r="G103">
-        <v>22.9</v>
+        <v>20.9</v>
       </c>
       <c r="H103">
-        <v>2.88</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="I103">
-        <v>0.80844999999999989</v>
+        <v>0.82269999999999999</v>
       </c>
       <c r="J103" t="s">
         <v>112</v>
@@ -10794,19 +10794,19 @@
         <v>14</v>
       </c>
       <c r="E104">
-        <v>0.28050000000000003</v>
+        <v>0.29017300000000001</v>
       </c>
       <c r="F104">
-        <v>1923</v>
+        <v>1726</v>
       </c>
       <c r="G104">
-        <v>22.9</v>
+        <v>20.9</v>
       </c>
       <c r="H104">
-        <v>2.88</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="I104">
-        <v>0.80844999999999989</v>
+        <v>0.82269999999999999</v>
       </c>
       <c r="J104" t="s">
         <v>113</v>
@@ -10850,19 +10850,19 @@
         <v>14</v>
       </c>
       <c r="E105">
-        <v>0.28050000000000003</v>
+        <v>0.29017300000000001</v>
       </c>
       <c r="F105">
-        <v>1923</v>
+        <v>1726</v>
       </c>
       <c r="G105">
-        <v>22.9</v>
+        <v>20.9</v>
       </c>
       <c r="H105">
-        <v>2.88</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="I105">
-        <v>0.80844999999999989</v>
+        <v>0.82269999999999999</v>
       </c>
       <c r="J105" t="s">
         <v>114</v>
@@ -10906,19 +10906,19 @@
         <v>14</v>
       </c>
       <c r="E106">
-        <v>0.28050000000000003</v>
+        <v>0.29017300000000001</v>
       </c>
       <c r="F106">
-        <v>1923</v>
+        <v>1726</v>
       </c>
       <c r="G106">
-        <v>22.9</v>
+        <v>20.9</v>
       </c>
       <c r="H106">
-        <v>2.88</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="I106">
-        <v>0.80844999999999989</v>
+        <v>0.82269999999999999</v>
       </c>
       <c r="J106" t="s">
         <v>115</v>
@@ -10962,7 +10962,7 @@
         <v>14</v>
       </c>
       <c r="E107">
-        <v>0.33377500000000004</v>
+        <v>0.33711275000000002</v>
       </c>
       <c r="F107">
         <v>1726</v>
@@ -11018,7 +11018,7 @@
         <v>14</v>
       </c>
       <c r="E108">
-        <v>0.35067499999999996</v>
+        <v>0.35418174999999996</v>
       </c>
       <c r="F108">
         <v>1726</v>
@@ -11074,19 +11074,19 @@
         <v>14</v>
       </c>
       <c r="E109">
-        <v>0.28050000000000003</v>
+        <v>0.29017300000000001</v>
       </c>
       <c r="F109">
-        <v>1923</v>
+        <v>1726</v>
       </c>
       <c r="G109">
-        <v>22.9</v>
+        <v>20.9</v>
       </c>
       <c r="H109">
-        <v>2.88</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="I109">
-        <v>0.80844999999999989</v>
+        <v>0.82269999999999999</v>
       </c>
       <c r="J109" t="s">
         <v>118</v>
@@ -11130,19 +11130,19 @@
         <v>14</v>
       </c>
       <c r="E110">
-        <v>0.28050000000000003</v>
+        <v>0.29017300000000001</v>
       </c>
       <c r="F110">
-        <v>1923</v>
+        <v>1726</v>
       </c>
       <c r="G110">
-        <v>22.9</v>
+        <v>20.9</v>
       </c>
       <c r="H110">
-        <v>2.88</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="I110">
-        <v>0.80844999999999989</v>
+        <v>0.82269999999999999</v>
       </c>
       <c r="J110" t="s">
         <v>119</v>
@@ -11186,7 +11186,7 @@
         <v>14</v>
       </c>
       <c r="E111">
-        <v>0.35067499999999996</v>
+        <v>0.35418174999999996</v>
       </c>
       <c r="F111">
         <v>1726</v>
@@ -11242,7 +11242,7 @@
         <v>14</v>
       </c>
       <c r="E112">
-        <v>0.35067499999999996</v>
+        <v>0.35418174999999996</v>
       </c>
       <c r="F112">
         <v>1726</v>
@@ -11298,7 +11298,7 @@
         <v>14</v>
       </c>
       <c r="E113">
-        <v>0.31264999999999998</v>
+        <v>0.31577649999999996</v>
       </c>
       <c r="F113">
         <v>1726</v>
@@ -11354,7 +11354,7 @@
         <v>14</v>
       </c>
       <c r="E114">
-        <v>0.31264999999999998</v>
+        <v>0.31577649999999996</v>
       </c>
       <c r="F114">
         <v>1726</v>
@@ -11410,7 +11410,7 @@
         <v>14</v>
       </c>
       <c r="E115">
-        <v>0.35067499999999996</v>
+        <v>0.35418174999999996</v>
       </c>
       <c r="F115">
         <v>1726</v>
@@ -11466,7 +11466,7 @@
         <v>14</v>
       </c>
       <c r="E116">
-        <v>0.12615999999999999</v>
+        <v>0.1274216</v>
       </c>
       <c r="F116">
         <v>3583</v>
@@ -11522,7 +11522,7 @@
         <v>14</v>
       </c>
       <c r="E117">
-        <v>0.12615999999999999</v>
+        <v>0.1274216</v>
       </c>
       <c r="F117">
         <v>3583</v>
@@ -11578,7 +11578,7 @@
         <v>14</v>
       </c>
       <c r="E118">
-        <v>0.12615999999999999</v>
+        <v>0.1274216</v>
       </c>
       <c r="F118">
         <v>3583</v>
@@ -11634,7 +11634,7 @@
         <v>14</v>
       </c>
       <c r="E119">
-        <v>0.12615999999999999</v>
+        <v>0.1274216</v>
       </c>
       <c r="F119">
         <v>3583</v>
@@ -11690,7 +11690,7 @@
         <v>14</v>
       </c>
       <c r="E120">
-        <v>0.12615999999999999</v>
+        <v>0.1274216</v>
       </c>
       <c r="F120">
         <v>3583</v>
@@ -11746,7 +11746,7 @@
         <v>14</v>
       </c>
       <c r="E121">
-        <v>0.12615999999999999</v>
+        <v>0.1274216</v>
       </c>
       <c r="F121">
         <v>3583</v>
@@ -11802,7 +11802,7 @@
         <v>14</v>
       </c>
       <c r="E122">
-        <v>0.12615999999999999</v>
+        <v>0.1274216</v>
       </c>
       <c r="F122">
         <v>3583</v>
@@ -11858,7 +11858,7 @@
         <v>14</v>
       </c>
       <c r="E123">
-        <v>0.12615999999999999</v>
+        <v>0.1274216</v>
       </c>
       <c r="F123">
         <v>3583</v>
@@ -11914,7 +11914,7 @@
         <v>14</v>
       </c>
       <c r="E124">
-        <v>0.12615999999999999</v>
+        <v>0.1274216</v>
       </c>
       <c r="F124">
         <v>3583</v>
@@ -11970,7 +11970,7 @@
         <v>14</v>
       </c>
       <c r="E125">
-        <v>0.12615999999999999</v>
+        <v>0.1274216</v>
       </c>
       <c r="F125">
         <v>3583</v>
@@ -12026,7 +12026,7 @@
         <v>14</v>
       </c>
       <c r="E126">
-        <v>0.12615999999999999</v>
+        <v>0.1274216</v>
       </c>
       <c r="F126">
         <v>3583</v>
@@ -12082,7 +12082,7 @@
         <v>14</v>
       </c>
       <c r="E127">
-        <v>0.12615999999999999</v>
+        <v>0.1274216</v>
       </c>
       <c r="F127">
         <v>3583</v>
@@ -12138,7 +12138,7 @@
         <v>14</v>
       </c>
       <c r="E128">
-        <v>0.12615999999999999</v>
+        <v>0.1274216</v>
       </c>
       <c r="F128">
         <v>3583</v>
@@ -12194,7 +12194,7 @@
         <v>14</v>
       </c>
       <c r="E129">
-        <v>0.12615999999999999</v>
+        <v>0.1274216</v>
       </c>
       <c r="F129">
         <v>3583</v>
@@ -12250,7 +12250,7 @@
         <v>14</v>
       </c>
       <c r="E130">
-        <v>0.12615999999999999</v>
+        <v>0.1274216</v>
       </c>
       <c r="F130">
         <v>3583</v>
@@ -12306,7 +12306,7 @@
         <v>14</v>
       </c>
       <c r="E131">
-        <v>0.12615999999999999</v>
+        <v>0.1274216</v>
       </c>
       <c r="F131">
         <v>3583</v>
@@ -12362,7 +12362,7 @@
         <v>14</v>
       </c>
       <c r="E132">
-        <v>0.12615999999999999</v>
+        <v>0.1274216</v>
       </c>
       <c r="F132">
         <v>3583</v>
@@ -12418,7 +12418,7 @@
         <v>14</v>
       </c>
       <c r="E133">
-        <v>0.12615999999999999</v>
+        <v>0.1274216</v>
       </c>
       <c r="F133">
         <v>3583</v>
@@ -12474,7 +12474,7 @@
         <v>14</v>
       </c>
       <c r="E134">
-        <v>0.12615999999999999</v>
+        <v>0.1274216</v>
       </c>
       <c r="F134">
         <v>3583</v>
@@ -12530,7 +12530,7 @@
         <v>14</v>
       </c>
       <c r="E135">
-        <v>0.13224000000000002</v>
+        <v>0.13356240000000003</v>
       </c>
       <c r="F135">
         <v>3583</v>
@@ -25986,7 +25986,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D04CDF2F-C866-48BE-8011-A12F25D410B0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE8F245C-8A00-4630-BBDC-EF982FCC0C47}">
   <dimension ref="B9:T1313"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -26071,7 +26071,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
       <c r="G11">
-        <v>0.21</v>
+        <v>0.21209999999999998</v>
       </c>
       <c r="H11">
         <v>4725</v>
@@ -26124,7 +26124,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
       <c r="G12">
-        <v>0.23</v>
+        <v>0.23230000000000003</v>
       </c>
       <c r="H12">
         <v>4725</v>
@@ -26177,7 +26177,7 @@
         <v>0.04</v>
       </c>
       <c r="G13">
-        <v>0.23000000000000004</v>
+        <v>0.23230000000000001</v>
       </c>
       <c r="H13">
         <v>4725</v>
@@ -26230,7 +26230,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
       <c r="G14">
-        <v>0.23</v>
+        <v>0.23230000000000001</v>
       </c>
       <c r="H14">
         <v>4725</v>
@@ -26283,7 +26283,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
       <c r="G15">
-        <v>0.23</v>
+        <v>0.23230000000000003</v>
       </c>
       <c r="H15">
         <v>4725</v>
@@ -26336,7 +26336,7 @@
         <v>8.8999999999999996E-2</v>
       </c>
       <c r="G16">
-        <v>0.22999999999999998</v>
+        <v>0.23230000000000001</v>
       </c>
       <c r="H16">
         <v>4725</v>
@@ -26389,7 +26389,7 @@
         <v>0.105</v>
       </c>
       <c r="G17">
-        <v>0.23</v>
+        <v>0.23230000000000001</v>
       </c>
       <c r="H17">
         <v>4725</v>
@@ -26442,7 +26442,7 @@
         <v>3.9E-2</v>
       </c>
       <c r="G18">
-        <v>0.23</v>
+        <v>0.23229999999999998</v>
       </c>
       <c r="H18">
         <v>4725</v>
@@ -26495,7 +26495,7 @@
         <v>0.03</v>
       </c>
       <c r="G19">
-        <v>0.23999999999999996</v>
+        <v>0.2424</v>
       </c>
       <c r="H19">
         <v>4725</v>
@@ -26548,7 +26548,7 @@
         <v>0.03</v>
       </c>
       <c r="G20">
-        <v>0.23999999999999996</v>
+        <v>0.2424</v>
       </c>
       <c r="H20">
         <v>4725</v>
@@ -26601,7 +26601,7 @@
         <v>0.03</v>
       </c>
       <c r="G21">
-        <v>0.23999999999999996</v>
+        <v>0.2424</v>
       </c>
       <c r="H21">
         <v>4725</v>
@@ -26654,7 +26654,7 @@
         <v>0.17199999999999999</v>
       </c>
       <c r="G22">
-        <v>0.24000000000000002</v>
+        <v>0.24239999999999998</v>
       </c>
       <c r="H22">
         <v>4725</v>
@@ -26707,7 +26707,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
       <c r="G23">
-        <v>0.24000000000000002</v>
+        <v>0.2424</v>
       </c>
       <c r="H23">
         <v>4725</v>
@@ -26760,7 +26760,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
       <c r="G24">
-        <v>0.24</v>
+        <v>0.24240000000000003</v>
       </c>
       <c r="H24">
         <v>4725</v>
@@ -26813,7 +26813,7 @@
         <v>8.5000000000000006E-2</v>
       </c>
       <c r="G25">
-        <v>0.24</v>
+        <v>0.2424</v>
       </c>
       <c r="H25">
         <v>4725</v>
@@ -26866,7 +26866,7 @@
         <v>0.17799999999999999</v>
       </c>
       <c r="G26">
-        <v>0.24</v>
+        <v>0.24239999999999998</v>
       </c>
       <c r="H26">
         <v>4725</v>
@@ -26919,7 +26919,7 @@
         <v>0.23300000000000001</v>
       </c>
       <c r="G27">
-        <v>0.24499999999999997</v>
+        <v>0.24745</v>
       </c>
       <c r="H27">
         <v>4725</v>
@@ -26972,7 +26972,7 @@
         <v>0.161</v>
       </c>
       <c r="G28">
-        <v>0.24499999999999997</v>
+        <v>0.24745</v>
       </c>
       <c r="H28">
         <v>4725</v>
@@ -27025,7 +27025,7 @@
         <v>0.11899999999999999</v>
       </c>
       <c r="G29">
-        <v>0.24500000000000002</v>
+        <v>0.24745</v>
       </c>
       <c r="H29">
         <v>4725</v>
@@ -27078,7 +27078,7 @@
         <v>0.158</v>
       </c>
       <c r="G30">
-        <v>0.245</v>
+        <v>0.24744999999999998</v>
       </c>
       <c r="H30">
         <v>4725</v>
@@ -27131,7 +27131,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
       <c r="G31">
-        <v>0.245</v>
+        <v>0.24745000000000003</v>
       </c>
       <c r="H31">
         <v>4725</v>
@@ -27184,7 +27184,7 @@
         <v>0.16300000000000001</v>
       </c>
       <c r="G32">
-        <v>0.24499999999999997</v>
+        <v>0.24745</v>
       </c>
       <c r="H32">
         <v>4725</v>
@@ -27237,7 +27237,7 @@
         <v>0.26700000000000002</v>
       </c>
       <c r="G33">
-        <v>0.24500000000000002</v>
+        <v>0.24745000000000003</v>
       </c>
       <c r="H33">
         <v>4725</v>
@@ -27290,7 +27290,7 @@
         <v>0.106</v>
       </c>
       <c r="G34">
-        <v>0.245</v>
+        <v>0.24745</v>
       </c>
       <c r="H34">
         <v>4725</v>
@@ -27343,7 +27343,7 @@
         <v>0.193</v>
       </c>
       <c r="G35">
-        <v>0.255</v>
+        <v>0.25755</v>
       </c>
       <c r="H35">
         <v>4725</v>
@@ -27396,7 +27396,7 @@
         <v>0.126</v>
       </c>
       <c r="G36">
-        <v>0.25499999999999995</v>
+        <v>0.25755</v>
       </c>
       <c r="H36">
         <v>4725</v>
@@ -27449,7 +27449,7 @@
         <v>0.113</v>
       </c>
       <c r="G37">
-        <v>0.255</v>
+        <v>0.25755</v>
       </c>
       <c r="H37">
         <v>4725</v>
@@ -27502,7 +27502,7 @@
         <v>0.124</v>
       </c>
       <c r="G38">
-        <v>0.255</v>
+        <v>0.25755</v>
       </c>
       <c r="H38">
         <v>4725</v>
@@ -27555,7 +27555,7 @@
         <v>0.04</v>
       </c>
       <c r="G39">
-        <v>0.255</v>
+        <v>0.25755</v>
       </c>
       <c r="H39">
         <v>4725</v>
@@ -27608,7 +27608,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
       <c r="G40">
-        <v>0.255</v>
+        <v>0.25755</v>
       </c>
       <c r="H40">
         <v>4725</v>
@@ -27661,7 +27661,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
       <c r="G41">
-        <v>0.28000000000000003</v>
+        <v>0.28280000000000005</v>
       </c>
       <c r="H41">
         <v>4725</v>
@@ -27714,7 +27714,7 @@
         <v>0.11700000000000001</v>
       </c>
       <c r="G42">
-        <v>0.3</v>
+        <v>0.30299999999999999</v>
       </c>
       <c r="H42">
         <v>4725</v>
@@ -27767,7 +27767,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
       <c r="G43">
-        <v>0.3</v>
+        <v>0.30299999999999999</v>
       </c>
       <c r="H43">
         <v>4725</v>
@@ -27820,7 +27820,7 @@
         <v>6.9000000000000006E-2</v>
       </c>
       <c r="G44">
-        <v>0.3</v>
+        <v>0.30299999999999999</v>
       </c>
       <c r="H44">
         <v>4725</v>
@@ -27873,7 +27873,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
       <c r="G45">
-        <v>0.3</v>
+        <v>0.30299999999999999</v>
       </c>
       <c r="H45">
         <v>4725</v>
@@ -27926,7 +27926,7 @@
         <v>0.04</v>
       </c>
       <c r="G46">
-        <v>0.3</v>
+        <v>0.30299999999999999</v>
       </c>
       <c r="H46">
         <v>4725</v>
@@ -27979,7 +27979,7 @@
         <v>4.3999999999999997E-2</v>
       </c>
       <c r="G47">
-        <v>0.3</v>
+        <v>0.30299999999999999</v>
       </c>
       <c r="H47">
         <v>4725</v>
@@ -28032,7 +28032,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
       <c r="G48">
-        <v>0.32</v>
+        <v>0.32319999999999999</v>
       </c>
       <c r="H48">
         <v>4725</v>
@@ -28085,7 +28085,7 @@
         <v>6.4870000000000001</v>
       </c>
       <c r="G49">
-        <v>0.35</v>
+        <v>0.35350000000000004</v>
       </c>
       <c r="H49">
         <v>3500</v>
@@ -28138,7 +28138,7 @@
         <v>6.9000000000000006E-2</v>
       </c>
       <c r="G50">
-        <v>0.26500000000000001</v>
+        <v>0.26765</v>
       </c>
       <c r="H50">
         <v>4024.9999999999991</v>
@@ -28191,7 +28191,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="G51">
-        <v>0.31</v>
+        <v>0.31309999999999999</v>
       </c>
       <c r="H51">
         <v>4024.9999999999991</v>
@@ -28244,7 +28244,7 @@
         <v>5.8000000000000003E-2</v>
       </c>
       <c r="G52">
-        <v>0.31</v>
+        <v>0.31309999999999999</v>
       </c>
       <c r="H52">
         <v>4024.9999999999995</v>
@@ -28297,7 +28297,7 @@
         <v>5.8000000000000003E-2</v>
       </c>
       <c r="G53">
-        <v>0.31</v>
+        <v>0.31309999999999999</v>
       </c>
       <c r="H53">
         <v>4024.9999999999995</v>
@@ -28350,7 +28350,7 @@
         <v>6.4000000000000001E-2</v>
       </c>
       <c r="G54">
-        <v>0.255</v>
+        <v>0.25755</v>
       </c>
       <c r="H54">
         <v>4024.9999999999995</v>
@@ -28403,7 +28403,7 @@
         <v>0.05</v>
       </c>
       <c r="G55">
-        <v>0.3</v>
+        <v>0.30299999999999999</v>
       </c>
       <c r="H55">
         <v>4725</v>
@@ -28456,7 +28456,7 @@
         <v>5.0999999999999997E-2</v>
       </c>
       <c r="G56">
-        <v>0.28999999999999998</v>
+        <v>0.29289999999999999</v>
       </c>
       <c r="H56">
         <v>4024.9999999999995</v>
@@ -28509,7 +28509,7 @@
         <v>6.8000000000000005E-2</v>
       </c>
       <c r="G57">
-        <v>0.26500000000000001</v>
+        <v>0.26765</v>
       </c>
       <c r="H57">
         <v>4024.9999999999991</v>
@@ -28562,7 +28562,7 @@
         <v>0.114</v>
       </c>
       <c r="G58">
-        <v>0.30999999999999994</v>
+        <v>0.31309999999999999</v>
       </c>
       <c r="H58">
         <v>4024.9999999999995</v>
@@ -28615,7 +28615,7 @@
         <v>6.2E-2</v>
       </c>
       <c r="G59">
-        <v>0.255</v>
+        <v>0.25755</v>
       </c>
       <c r="H59">
         <v>4024.9999999999995</v>
@@ -28668,7 +28668,7 @@
         <v>0.06</v>
       </c>
       <c r="G60">
-        <v>0.31</v>
+        <v>0.31309999999999999</v>
       </c>
       <c r="H60">
         <v>4024.9999999999995</v>
@@ -28721,7 +28721,7 @@
         <v>0.05</v>
       </c>
       <c r="G61">
-        <v>0.245</v>
+        <v>0.24745</v>
       </c>
       <c r="H61">
         <v>4725</v>
@@ -28774,7 +28774,7 @@
         <v>0.05</v>
       </c>
       <c r="G62">
-        <v>0.245</v>
+        <v>0.24745</v>
       </c>
       <c r="H62">
         <v>4725</v>
@@ -28827,7 +28827,7 @@
         <v>6.4000000000000001E-2</v>
       </c>
       <c r="G63">
-        <v>0.28999999999999998</v>
+        <v>0.29289999999999999</v>
       </c>
       <c r="H63">
         <v>4024.9999999999995</v>
@@ -28880,7 +28880,7 @@
         <v>0.06</v>
       </c>
       <c r="G64">
-        <v>0.255</v>
+        <v>0.25755</v>
       </c>
       <c r="H64">
         <v>4024.9999999999995</v>
@@ -28933,7 +28933,7 @@
         <v>6.7000000000000004E-2</v>
       </c>
       <c r="G65">
-        <v>0.255</v>
+        <v>0.25755</v>
       </c>
       <c r="H65">
         <v>4024.9999999999991</v>
@@ -28986,7 +28986,7 @@
         <v>5.2999999999999999E-2</v>
       </c>
       <c r="G66">
-        <v>0.26500000000000001</v>
+        <v>0.26765</v>
       </c>
       <c r="H66">
         <v>4024.9999999999995</v>
@@ -29039,7 +29039,7 @@
         <v>5.3999999999999999E-2</v>
       </c>
       <c r="G67">
-        <v>0.255</v>
+        <v>0.25755</v>
       </c>
       <c r="H67">
         <v>4024.9999999999995</v>
@@ -29092,7 +29092,7 @@
         <v>6.6000000000000003E-2</v>
       </c>
       <c r="G68">
-        <v>0.26500000000000001</v>
+        <v>0.26765</v>
       </c>
       <c r="H68">
         <v>4024.9999999999991</v>
@@ -29145,7 +29145,7 @@
         <v>0.06</v>
       </c>
       <c r="G69">
-        <v>0.255</v>
+        <v>0.25755</v>
       </c>
       <c r="H69">
         <v>4024.9999999999995</v>
@@ -29198,7 +29198,7 @@
         <v>0.05</v>
       </c>
       <c r="G70">
-        <v>0.23</v>
+        <v>0.23230000000000001</v>
       </c>
       <c r="H70">
         <v>4725</v>
@@ -29251,7 +29251,7 @@
         <v>0.05</v>
       </c>
       <c r="G71">
-        <v>0.23</v>
+        <v>0.23230000000000001</v>
       </c>
       <c r="H71">
         <v>4725</v>
@@ -29304,7 +29304,7 @@
         <v>5.0999999999999997E-2</v>
       </c>
       <c r="G72">
-        <v>0.23</v>
+        <v>0.23230000000000001</v>
       </c>
       <c r="H72">
         <v>4024.9999999999995</v>
@@ -29357,7 +29357,7 @@
         <v>6.4000000000000001E-2</v>
       </c>
       <c r="G73">
-        <v>0.255</v>
+        <v>0.25755</v>
       </c>
       <c r="H73">
         <v>4024.9999999999995</v>
@@ -29410,7 +29410,7 @@
         <v>7.9000000000000001E-2</v>
       </c>
       <c r="G74">
-        <v>0.255</v>
+        <v>0.25755</v>
       </c>
       <c r="H74">
         <v>4024.9999999999991</v>
@@ -29463,7 +29463,7 @@
         <v>8.2000000000000003E-2</v>
       </c>
       <c r="G75">
-        <v>0.31</v>
+        <v>0.31309999999999999</v>
       </c>
       <c r="H75">
         <v>4024.9999999999991</v>
@@ -29516,7 +29516,7 @@
         <v>0.05</v>
       </c>
       <c r="G76">
-        <v>0.245</v>
+        <v>0.24745</v>
       </c>
       <c r="H76">
         <v>4725</v>
@@ -29569,7 +29569,7 @@
         <v>6.2E-2</v>
       </c>
       <c r="G77">
-        <v>0.23</v>
+        <v>0.23230000000000001</v>
       </c>
       <c r="H77">
         <v>4024.9999999999995</v>
@@ -29622,7 +29622,7 @@
         <v>6.0999999999999999E-2</v>
       </c>
       <c r="G78">
-        <v>0.26500000000000001</v>
+        <v>0.26765</v>
       </c>
       <c r="H78">
         <v>4024.9999999999995</v>
@@ -29675,7 +29675,7 @@
         <v>8.7999999999999995E-2</v>
       </c>
       <c r="G79">
-        <v>0.28999999999999998</v>
+        <v>0.29289999999999999</v>
       </c>
       <c r="H79">
         <v>4024.9999999999995</v>
@@ -29728,7 +29728,7 @@
         <v>0.06</v>
       </c>
       <c r="G80">
-        <v>0.255</v>
+        <v>0.25755</v>
       </c>
       <c r="H80">
         <v>4024.9999999999995</v>
@@ -29781,7 +29781,7 @@
         <v>0.05</v>
       </c>
       <c r="G81">
-        <v>0.28000000000000003</v>
+        <v>0.28280000000000005</v>
       </c>
       <c r="H81">
         <v>4725</v>
@@ -29834,7 +29834,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="G82">
-        <v>0.26500000000000001</v>
+        <v>0.26765</v>
       </c>
       <c r="H82">
         <v>4024.9999999999995</v>
@@ -29887,7 +29887,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="G83">
-        <v>0.26500000000000001</v>
+        <v>0.26765</v>
       </c>
       <c r="H83">
         <v>4024.9999999999991</v>
@@ -29940,7 +29940,7 @@
         <v>5.3999999999999999E-2</v>
       </c>
       <c r="G84">
-        <v>0.28999999999999998</v>
+        <v>0.29289999999999999</v>
       </c>
       <c r="H84">
         <v>4024.9999999999995</v>
@@ -29993,7 +29993,7 @@
         <v>7.1999999999999995E-2</v>
       </c>
       <c r="G85">
-        <v>0.25</v>
+        <v>0.2525</v>
       </c>
       <c r="H85">
         <v>4024.9999999999991</v>
@@ -30046,7 +30046,7 @@
         <v>6.0999999999999999E-2</v>
       </c>
       <c r="G86">
-        <v>0.255</v>
+        <v>0.25755</v>
       </c>
       <c r="H86">
         <v>4024.9999999999995</v>
@@ -30099,7 +30099,7 @@
         <v>6.8000000000000005E-2</v>
       </c>
       <c r="G87">
-        <v>0.25</v>
+        <v>0.2525</v>
       </c>
       <c r="H87">
         <v>4024.9999999999991</v>
@@ -30152,7 +30152,7 @@
         <v>0.05</v>
       </c>
       <c r="G88">
-        <v>0.255</v>
+        <v>0.25755</v>
       </c>
       <c r="H88">
         <v>4725</v>
@@ -30205,7 +30205,7 @@
         <v>7.0999999999999994E-2</v>
       </c>
       <c r="G89">
-        <v>0.26500000000000001</v>
+        <v>0.26765</v>
       </c>
       <c r="H89">
         <v>4024.9999999999991</v>
@@ -30258,7 +30258,7 @@
         <v>5.6000000000000001E-2</v>
       </c>
       <c r="G90">
-        <v>0.255</v>
+        <v>0.25755</v>
       </c>
       <c r="H90">
         <v>4024.9999999999995</v>
@@ -30311,7 +30311,7 @@
         <v>0.06</v>
       </c>
       <c r="G91">
-        <v>0.255</v>
+        <v>0.25755</v>
       </c>
       <c r="H91">
         <v>4024.9999999999995</v>
@@ -30364,7 +30364,7 @@
         <v>7.0999999999999994E-2</v>
       </c>
       <c r="G92">
-        <v>0.26500000000000001</v>
+        <v>0.26765</v>
       </c>
       <c r="H92">
         <v>4024.9999999999991</v>
@@ -30417,7 +30417,7 @@
         <v>8.3000000000000004E-2</v>
       </c>
       <c r="G93">
-        <v>0.26500000000000001</v>
+        <v>0.26765</v>
       </c>
       <c r="H93">
         <v>4024.9999999999991</v>
@@ -30470,7 +30470,7 @@
         <v>9.9000000000000005E-2</v>
       </c>
       <c r="G94">
-        <v>0.26500000000000001</v>
+        <v>0.26765</v>
       </c>
       <c r="H94">
         <v>4024.9999999999995</v>
@@ -30523,7 +30523,7 @@
         <v>6.2E-2</v>
       </c>
       <c r="G95">
-        <v>0.255</v>
+        <v>0.25755</v>
       </c>
       <c r="H95">
         <v>4024.9999999999995</v>
@@ -30576,7 +30576,7 @@
         <v>0.05</v>
       </c>
       <c r="G96">
-        <v>0.23</v>
+        <v>0.23230000000000001</v>
       </c>
       <c r="H96">
         <v>4725</v>
@@ -30629,7 +30629,7 @@
         <v>7.0999999999999994E-2</v>
       </c>
       <c r="G97">
-        <v>0.26500000000000001</v>
+        <v>0.26765</v>
       </c>
       <c r="H97">
         <v>4024.9999999999991</v>
@@ -30682,7 +30682,7 @@
         <v>5.3999999999999999E-2</v>
       </c>
       <c r="G98">
-        <v>0.255</v>
+        <v>0.25755</v>
       </c>
       <c r="H98">
         <v>4024.9999999999995</v>
@@ -30735,7 +30735,7 @@
         <v>7.6999999999999999E-2</v>
       </c>
       <c r="G99">
-        <v>0.255</v>
+        <v>0.25755</v>
       </c>
       <c r="H99">
         <v>4024.9999999999991</v>
@@ -30788,7 +30788,7 @@
         <v>5.5E-2</v>
       </c>
       <c r="G100">
-        <v>0.31</v>
+        <v>0.31309999999999993</v>
       </c>
       <c r="H100">
         <v>4024.9999999999995</v>
@@ -30841,7 +30841,7 @@
         <v>5.1999999999999998E-2</v>
       </c>
       <c r="G101">
-        <v>0.31</v>
+        <v>0.31309999999999999</v>
       </c>
       <c r="H101">
         <v>4024.9999999999995</v>
@@ -30894,7 +30894,7 @@
         <v>5.8000000000000003E-2</v>
       </c>
       <c r="G102">
-        <v>0.31</v>
+        <v>0.31309999999999999</v>
       </c>
       <c r="H102">
         <v>4024.9999999999995</v>
@@ -30947,7 +30947,7 @@
         <v>9.6000000000000002E-2</v>
       </c>
       <c r="G103">
-        <v>0.31</v>
+        <v>0.31309999999999999</v>
       </c>
       <c r="H103">
         <v>4024.9999999999995</v>
@@ -31000,7 +31000,7 @@
         <v>0.11600000000000001</v>
       </c>
       <c r="G104">
-        <v>0.31</v>
+        <v>0.31309999999999999</v>
       </c>
       <c r="H104">
         <v>4024.9999999999995</v>
@@ -31053,7 +31053,7 @@
         <v>5.0999999999999997E-2</v>
       </c>
       <c r="G105">
-        <v>0.255</v>
+        <v>0.25755</v>
       </c>
       <c r="H105">
         <v>4024.9999999999995</v>
@@ -31106,7 +31106,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="G106">
-        <v>0.31</v>
+        <v>0.31309999999999999</v>
       </c>
       <c r="H106">
         <v>4024.9999999999991</v>
@@ -31159,7 +31159,7 @@
         <v>5.3999999999999999E-2</v>
       </c>
       <c r="G107">
-        <v>0.26500000000000001</v>
+        <v>0.26765</v>
       </c>
       <c r="H107">
         <v>4024.9999999999995</v>
@@ -31212,7 +31212,7 @@
         <v>6.2E-2</v>
       </c>
       <c r="G108">
-        <v>0.255</v>
+        <v>0.25755</v>
       </c>
       <c r="H108">
         <v>4024.9999999999995</v>
@@ -31265,7 +31265,7 @@
         <v>6.2E-2</v>
       </c>
       <c r="G109">
-        <v>0.255</v>
+        <v>0.25755</v>
       </c>
       <c r="H109">
         <v>4024.9999999999995</v>
@@ -31318,7 +31318,7 @@
         <v>0.08</v>
       </c>
       <c r="G110">
-        <v>0.26500000000000001</v>
+        <v>0.26765</v>
       </c>
       <c r="H110">
         <v>4024.9999999999991</v>
@@ -31371,7 +31371,7 @@
         <v>0.70399999999999996</v>
       </c>
       <c r="G111">
-        <v>0.36499999999999999</v>
+        <v>0.36864999999999992</v>
       </c>
       <c r="H111">
         <v>2300</v>
@@ -31424,7 +31424,7 @@
         <v>0.80449999999999999</v>
       </c>
       <c r="G112">
-        <v>0.40824114356743318</v>
+        <v>0.41232355500310752</v>
       </c>
       <c r="H112">
         <v>4570.4039776258542</v>
@@ -31477,7 +31477,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
       <c r="G113">
-        <v>0.27</v>
+        <v>0.2727</v>
       </c>
       <c r="H113">
         <v>2700</v>
@@ -31530,7 +31530,7 @@
         <v>0.52500000000000002</v>
       </c>
       <c r="G114">
-        <v>0.28000000000000003</v>
+        <v>0.28280000000000005</v>
       </c>
       <c r="H114">
         <v>2300</v>
@@ -31583,7 +31583,7 @@
         <v>1.4</v>
       </c>
       <c r="G115">
-        <v>0.28000000000000003</v>
+        <v>0.28280000000000005</v>
       </c>
       <c r="H115">
         <v>2300</v>
@@ -31636,7 +31636,7 @@
         <v>3.6054999999999993</v>
       </c>
       <c r="G116">
-        <v>0.27976979614477893</v>
+        <v>0.28256749410622678</v>
       </c>
       <c r="H116">
         <v>2309.2081542088481</v>
@@ -31689,7 +31689,7 @@
         <v>0.51729999999999998</v>
       </c>
       <c r="G117">
-        <v>0.28000000000000008</v>
+        <v>0.28280000000000005</v>
       </c>
       <c r="H117">
         <v>2300</v>
@@ -31742,7 +31742,7 @@
         <v>0.51</v>
       </c>
       <c r="G118">
-        <v>0.27911764705882358</v>
+        <v>0.28190882352941177</v>
       </c>
       <c r="H118">
         <v>2335.294117647059</v>
@@ -31795,7 +31795,7 @@
         <v>0.05</v>
       </c>
       <c r="G119">
-        <v>0.27</v>
+        <v>0.2727</v>
       </c>
       <c r="H119">
         <v>2700</v>
@@ -31848,7 +31848,7 @@
         <v>0.76880000000000004</v>
       </c>
       <c r="G120">
-        <v>0.297044745057232</v>
+        <v>0.30001519250780434</v>
       </c>
       <c r="H120">
         <v>2044.3288241415191</v>
@@ -31901,7 +31901,7 @@
         <v>0.39419999999999999</v>
       </c>
       <c r="G121">
-        <v>0.28000000000000003</v>
+        <v>0.28280000000000005</v>
       </c>
       <c r="H121">
         <v>2300</v>
@@ -31954,7 +31954,7 @@
         <v>0.58569999999999989</v>
       </c>
       <c r="G122">
-        <v>0.31240566843093737</v>
+        <v>0.31552972511524674</v>
       </c>
       <c r="H122">
         <v>2113.9149735359401</v>
@@ -32007,7 +32007,7 @@
         <v>0.46020000000000005</v>
       </c>
       <c r="G123">
-        <v>0.3</v>
+        <v>0.30299999999999994</v>
       </c>
       <c r="H123">
         <v>2300</v>
@@ -32060,7 +32060,7 @@
         <v>0.32800000000000001</v>
       </c>
       <c r="G124">
-        <v>0.3</v>
+        <v>0.30299999999999999</v>
       </c>
       <c r="H124">
         <v>2300</v>
@@ -32113,7 +32113,7 @@
         <v>0.39610000000000001</v>
       </c>
       <c r="G125">
-        <v>0.29999999999999993</v>
+        <v>0.30299999999999999</v>
       </c>
       <c r="H125">
         <v>2300</v>
@@ -32166,7 +32166,7 @@
         <v>2.2328999999999999</v>
       </c>
       <c r="G126">
-        <v>0.314714496842671</v>
+        <v>0.31786164181109766</v>
       </c>
       <c r="H126">
         <v>2079.2825473599355</v>
@@ -32219,7 +32219,7 @@
         <v>1.8224</v>
       </c>
       <c r="G127">
-        <v>0.31460711150131693</v>
+        <v>0.31775318261633001</v>
       </c>
       <c r="H127">
         <v>2080.8933274802457</v>
@@ -32272,7 +32272,7 @@
         <v>0.98350000000000004</v>
       </c>
       <c r="G128">
-        <v>0.32</v>
+        <v>0.32319999999999999</v>
       </c>
       <c r="H128">
         <v>2000</v>
@@ -32325,7 +32325,7 @@
         <v>2.1356999999999999</v>
       </c>
       <c r="G129">
-        <v>0.31556492016669008</v>
+        <v>0.31872056936835697</v>
       </c>
       <c r="H129">
         <v>2066.5261974996488</v>
@@ -32378,7 +32378,7 @@
         <v>0.57740000000000002</v>
       </c>
       <c r="G130">
-        <v>0.3</v>
+        <v>0.30300000000000005</v>
       </c>
       <c r="H130">
         <v>2300</v>
@@ -32431,7 +32431,7 @@
         <v>2.3248000000000002</v>
       </c>
       <c r="G131">
-        <v>0.31766001376462494</v>
+        <v>0.32083661390227119</v>
       </c>
       <c r="H131">
         <v>2035.0997935306261</v>
@@ -32484,7 +32484,7 @@
         <v>1.4407000000000001</v>
       </c>
       <c r="G132">
-        <v>0.34</v>
+        <v>0.34340000000000004</v>
       </c>
       <c r="H132">
         <v>2000</v>
@@ -32537,7 +32537,7 @@
         <v>3.1385000000000001</v>
       </c>
       <c r="G133">
-        <v>0.34</v>
+        <v>0.34340000000000009</v>
       </c>
       <c r="H133">
         <v>2000</v>
@@ -32590,7 +32590,7 @@
         <v>3.9432999999999998</v>
       </c>
       <c r="G134">
-        <v>0.33834605533436463</v>
+        <v>0.34172951588770833</v>
       </c>
       <c r="H134">
         <v>2024.8091699845309</v>
@@ -32643,7 +32643,7 @@
         <v>1.4084000000000001</v>
       </c>
       <c r="G135">
-        <v>0.33999999999999997</v>
+        <v>0.34340000000000004</v>
       </c>
       <c r="H135">
         <v>1999.9999999999998</v>
@@ -32696,7 +32696,7 @@
         <v>3.3041999999999998</v>
       </c>
       <c r="G136">
-        <v>0.34000000000000008</v>
+        <v>0.34340000000000009</v>
       </c>
       <c r="H136">
         <v>2000</v>
@@ -32749,7 +32749,7 @@
         <v>2.1543000000000001</v>
       </c>
       <c r="G137">
-        <v>0.33581302511256556</v>
+        <v>0.33917115536369119</v>
       </c>
       <c r="H137">
         <v>2062.8046233115165</v>
@@ -32802,7 +32802,7 @@
         <v>6.2721</v>
       </c>
       <c r="G138">
-        <v>0.33970823169273451</v>
+        <v>0.34310531400966182</v>
       </c>
       <c r="H138">
         <v>2004.3765246089824</v>
@@ -32855,7 +32855,7 @@
         <v>6.3064000000000009</v>
       </c>
       <c r="G139">
-        <v>0.34</v>
+        <v>0.34339999999999998</v>
       </c>
       <c r="H139">
         <v>1999.9999999999998</v>
@@ -32908,7 +32908,7 @@
         <v>5.8499000000000008</v>
       </c>
       <c r="G140">
-        <v>0.33930255218037914</v>
+        <v>0.34269557770218295</v>
       </c>
       <c r="H140">
         <v>2010.4617172943126</v>
@@ -32961,7 +32961,7 @@
         <v>8.7742000000000004</v>
       </c>
       <c r="G141">
-        <v>0.33952816211164544</v>
+        <v>0.3429234437327619</v>
       </c>
       <c r="H141">
         <v>2007.0775683253173</v>
@@ -33014,7 +33014,7 @@
         <v>7.3849999999999998</v>
       </c>
       <c r="G142">
-        <v>0.3476289776574138</v>
+        <v>0.35110526743398779</v>
       </c>
       <c r="H142">
         <v>2035.5653351387948</v>
@@ -33067,7 +33067,7 @@
         <v>7.6911000000000005</v>
       </c>
       <c r="G143">
-        <v>0.34971447517260207</v>
+        <v>0.35321161992432809</v>
       </c>
       <c r="H143">
         <v>2004.2828724109684</v>
@@ -33120,7 +33120,7 @@
         <v>4.9011000000000005</v>
       </c>
       <c r="G144">
-        <v>0.3492858745995796</v>
+        <v>0.35277873334557541</v>
       </c>
       <c r="H144">
         <v>2010.7118810063046</v>
@@ -33173,7 +33173,7 @@
         <v>6.3571999999999989</v>
       </c>
       <c r="G145">
-        <v>0.34907632290945706</v>
+        <v>0.35256708613855164</v>
       </c>
       <c r="H145">
         <v>2013.8551563581455</v>
@@ -33226,7 +33226,7 @@
         <v>4.9151999999999996</v>
       </c>
       <c r="G146">
-        <v>0.34882080078125</v>
+        <v>0.35230900878906252</v>
       </c>
       <c r="H146">
         <v>2017.68798828125</v>
@@ -33279,7 +33279,7 @@
         <v>3.6268000000000002</v>
       </c>
       <c r="G147">
-        <v>0.34999999999999992</v>
+        <v>0.35349999999999993</v>
       </c>
       <c r="H147">
         <v>2000</v>
@@ -33332,7 +33332,7 @@
         <v>1.4444999999999999</v>
       </c>
       <c r="G148">
-        <v>0.34667705088265832</v>
+        <v>0.35014382139148498</v>
       </c>
       <c r="H148">
         <v>2077.5354794046384</v>
@@ -33385,7 +33385,7 @@
         <v>0.6724</v>
       </c>
       <c r="G149">
-        <v>0.34183819155264727</v>
+        <v>0.34525657346817368</v>
       </c>
       <c r="H149">
         <v>2168.5306365258775</v>
@@ -33438,7 +33438,7 @@
         <v>0.75139999999999996</v>
       </c>
       <c r="G150">
-        <v>0.34816742081447966</v>
+        <v>0.35164909502262442</v>
       </c>
       <c r="H150">
         <v>2042.7601809954751</v>
@@ -33491,7 +33491,7 @@
         <v>1.831</v>
       </c>
       <c r="G151">
-        <v>0.34033752048061172</v>
+        <v>0.34374089568541782</v>
       </c>
       <c r="H151">
         <v>2157.0617149098853</v>
@@ -33544,7 +33544,7 @@
         <v>1.5650999999999999</v>
       </c>
       <c r="G152">
-        <v>0.35776883266244969</v>
+        <v>0.36134652098907416</v>
       </c>
       <c r="H152">
         <v>2033.4675100632548</v>
@@ -33597,7 +33597,7 @@
         <v>0.75570000000000004</v>
       </c>
       <c r="G153">
-        <v>0.35497948921529704</v>
+        <v>0.35852928410745005</v>
       </c>
       <c r="H153">
         <v>2075.3076617705437</v>
@@ -33650,7 +33650,7 @@
         <v>0.15280000000000002</v>
       </c>
       <c r="G154">
-        <v>0.33999999999999997</v>
+        <v>0.34339999999999998</v>
       </c>
       <c r="H154">
         <v>2300</v>
@@ -33703,7 +33703,7 @@
         <v>3.1E-2</v>
       </c>
       <c r="G155">
-        <v>0.33</v>
+        <v>0.33330000000000004</v>
       </c>
       <c r="H155">
         <v>2700</v>
@@ -33756,7 +33756,7 @@
         <v>1.298</v>
       </c>
       <c r="G156">
-        <v>0.35539907550077038</v>
+        <v>0.35895306625577811</v>
       </c>
       <c r="H156">
         <v>2074.984591679507</v>
@@ -33809,7 +33809,7 @@
         <v>1.3057999999999998</v>
       </c>
       <c r="G157">
-        <v>0.36</v>
+        <v>0.36359999999999998</v>
       </c>
       <c r="H157">
         <v>2000</v>
@@ -33862,7 +33862,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="G158">
-        <v>0.34</v>
+        <v>0.34340000000000004</v>
       </c>
       <c r="H158">
         <v>2300</v>
@@ -33915,7 +33915,7 @@
         <v>0.1011</v>
       </c>
       <c r="G159">
-        <v>0.34</v>
+        <v>0.34340000000000004</v>
       </c>
       <c r="H159">
         <v>2300</v>
@@ -33968,7 +33968,7 @@
         <v>1.0787</v>
       </c>
       <c r="G160">
-        <v>0.36</v>
+        <v>0.36359999999999998</v>
       </c>
       <c r="H160">
         <v>2000</v>
@@ -34021,7 +34021,7 @@
         <v>1.105</v>
       </c>
       <c r="G161">
-        <v>0.34</v>
+        <v>0.34340000000000009</v>
       </c>
       <c r="H161">
         <v>2300</v>
@@ -34074,7 +34074,7 @@
         <v>0.20799999999999999</v>
       </c>
       <c r="G162">
-        <v>0.33999999999999997</v>
+        <v>0.34340000000000004</v>
       </c>
       <c r="H162">
         <v>2300</v>
@@ -34127,7 +34127,7 @@
         <v>0.58499999999999996</v>
       </c>
       <c r="G163">
-        <v>0.36</v>
+        <v>0.36359999999999998</v>
       </c>
       <c r="H163">
         <v>2000</v>
@@ -34180,7 +34180,7 @@
         <v>0.43439999999999995</v>
       </c>
       <c r="G164">
-        <v>0.35516574585635358</v>
+        <v>0.35871740331491714</v>
       </c>
       <c r="H164">
         <v>2072.5138121546961</v>
@@ -34233,7 +34233,7 @@
         <v>0.57380000000000009</v>
       </c>
       <c r="G165">
-        <v>0.35596723597072144</v>
+        <v>0.35952690833042866</v>
       </c>
       <c r="H165">
         <v>2060.491460439177</v>
@@ -34286,7 +34286,7 @@
         <v>0.59099999999999997</v>
       </c>
       <c r="G166">
-        <v>0.36</v>
+        <v>0.36359999999999998</v>
       </c>
       <c r="H166">
         <v>2000</v>
@@ -34339,7 +34339,7 @@
         <v>0.98899999999999999</v>
       </c>
       <c r="G167">
-        <v>0.35318503538928209</v>
+        <v>0.35671688574317495</v>
       </c>
       <c r="H167">
         <v>2102.2244691607684</v>
@@ -34392,7 +34392,7 @@
         <v>1.9356</v>
       </c>
       <c r="G168">
-        <v>0.35576255424674519</v>
+        <v>0.3593201797892126</v>
       </c>
       <c r="H168">
         <v>2063.5616862988222</v>
@@ -34445,7 +34445,7 @@
         <v>0.90760000000000007</v>
       </c>
       <c r="G169">
-        <v>0.3558660202732481</v>
+        <v>0.35942468047598053</v>
       </c>
       <c r="H169">
         <v>2062.0096959012781</v>
@@ -34498,7 +34498,7 @@
         <v>1.032</v>
       </c>
       <c r="G170">
-        <v>0.3493798449612403</v>
+        <v>0.3528736434108527</v>
       </c>
       <c r="H170">
         <v>2159.3023255813955</v>
@@ -34551,7 +34551,7 @@
         <v>0.66800000000000004</v>
       </c>
       <c r="G171">
-        <v>0.36</v>
+        <v>0.36359999999999998</v>
       </c>
       <c r="H171">
         <v>2000</v>
@@ -34604,7 +34604,7 @@
         <v>0.05</v>
       </c>
       <c r="G172">
-        <v>0.33</v>
+        <v>0.33330000000000004</v>
       </c>
       <c r="H172">
         <v>2700</v>
@@ -34657,7 +34657,7 @@
         <v>15.808600000000069</v>
       </c>
       <c r="G173">
-        <v>0.36</v>
+        <v>0.36359999999999998</v>
       </c>
       <c r="H173">
         <v>2000</v>
@@ -34710,7 +34710,7 @@
         <v>0.09</v>
       </c>
       <c r="G174">
-        <v>0.28000000000000003</v>
+        <v>0.28280000000000005</v>
       </c>
       <c r="H174">
         <v>4140</v>
@@ -34763,7 +34763,7 @@
         <v>0.09</v>
       </c>
       <c r="G175">
-        <v>0.28000000000000003</v>
+        <v>0.28280000000000005</v>
       </c>
       <c r="H175">
         <v>4140</v>
@@ -34816,7 +34816,7 @@
         <v>0.871</v>
       </c>
       <c r="G176">
-        <v>0.34</v>
+        <v>0.34340000000000004</v>
       </c>
       <c r="H176">
         <v>2000</v>
@@ -34869,7 +34869,7 @@
         <v>0.9</v>
       </c>
       <c r="G177">
-        <v>0.35</v>
+        <v>0.35349999999999998</v>
       </c>
       <c r="H177">
         <v>2000</v>
@@ -34922,7 +34922,7 @@
         <v>0.9</v>
       </c>
       <c r="G178">
-        <v>0.35</v>
+        <v>0.35349999999999998</v>
       </c>
       <c r="H178">
         <v>2000</v>
@@ -34975,7 +34975,7 @@
         <v>0.878</v>
       </c>
       <c r="G179">
-        <v>0.36</v>
+        <v>0.36359999999999998</v>
       </c>
       <c r="H179">
         <v>2000</v>
@@ -35028,7 +35028,7 @@
         <v>0.89300000000000002</v>
       </c>
       <c r="G180">
-        <v>0.34999999999999992</v>
+        <v>0.35349999999999998</v>
       </c>
       <c r="H180">
         <v>2000</v>
@@ -35081,7 +35081,7 @@
         <v>0.95699999999999996</v>
       </c>
       <c r="G181">
-        <v>0.35</v>
+        <v>0.35349999999999998</v>
       </c>
       <c r="H181">
         <v>2000</v>
@@ -35134,7 +35134,7 @@
         <v>0.89279999999999993</v>
       </c>
       <c r="G182">
-        <v>0.34</v>
+        <v>0.34340000000000004</v>
       </c>
       <c r="H182">
         <v>2000</v>
@@ -35187,7 +35187,7 @@
         <v>0.89279999999999993</v>
       </c>
       <c r="G183">
-        <v>0.34</v>
+        <v>0.34340000000000004</v>
       </c>
       <c r="H183">
         <v>2000</v>
@@ -35240,7 +35240,7 @@
         <v>0.89100000000000001</v>
       </c>
       <c r="G184">
-        <v>0.35</v>
+        <v>0.35349999999999998</v>
       </c>
       <c r="H184">
         <v>2000</v>
@@ -35293,7 +35293,7 @@
         <v>0.89100000000000001</v>
       </c>
       <c r="G185">
-        <v>0.35</v>
+        <v>0.35349999999999998</v>
       </c>
       <c r="H185">
         <v>2000</v>
@@ -35346,7 +35346,7 @@
         <v>0.89100000000000001</v>
       </c>
       <c r="G186">
-        <v>0.35</v>
+        <v>0.35349999999999998</v>
       </c>
       <c r="H186">
         <v>2000</v>
@@ -35399,7 +35399,7 @@
         <v>0.93870000000000009</v>
       </c>
       <c r="G187">
-        <v>0.35</v>
+        <v>0.35349999999999998</v>
       </c>
       <c r="H187">
         <v>2000</v>
@@ -35452,7 +35452,7 @@
         <v>0.9</v>
       </c>
       <c r="G188">
-        <v>0.34</v>
+        <v>0.34340000000000004</v>
       </c>
       <c r="H188">
         <v>2000</v>
@@ -35505,7 +35505,7 @@
         <v>0.9</v>
       </c>
       <c r="G189">
-        <v>0.35</v>
+        <v>0.35349999999999998</v>
       </c>
       <c r="H189">
         <v>2000</v>
@@ -35558,7 +35558,7 @@
         <v>0.59839999999999993</v>
       </c>
       <c r="G190">
-        <v>0.3</v>
+        <v>0.30299999999999999</v>
       </c>
       <c r="H190">
         <v>2200</v>
@@ -35611,7 +35611,7 @@
         <v>2.7601000000000004</v>
       </c>
       <c r="G191">
-        <v>0.31999999999999995</v>
+        <v>0.32319999999999993</v>
       </c>
       <c r="H191">
         <v>2199.9999999999995</v>
@@ -35664,7 +35664,7 @@
         <v>1.1257000000000001</v>
       </c>
       <c r="G192">
-        <v>0.32</v>
+        <v>0.32319999999999999</v>
       </c>
       <c r="H192">
         <v>2200</v>
@@ -35717,7 +35717,7 @@
         <v>2.2565</v>
       </c>
       <c r="G193">
-        <v>0.32</v>
+        <v>0.32319999999999993</v>
       </c>
       <c r="H193">
         <v>2200</v>
@@ -35770,7 +35770,7 @@
         <v>1.8520000000000001</v>
       </c>
       <c r="G194">
-        <v>0.32000000000000006</v>
+        <v>0.32320000000000004</v>
       </c>
       <c r="H194">
         <v>2200</v>
@@ -35823,7 +35823,7 @@
         <v>5.246599999999999</v>
       </c>
       <c r="G195">
-        <v>0.34</v>
+        <v>0.34340000000000015</v>
       </c>
       <c r="H195">
         <v>2200.0000000000005</v>
@@ -35876,7 +35876,7 @@
         <v>2.2890999999999999</v>
       </c>
       <c r="G196">
-        <v>0.34000000000000008</v>
+        <v>0.34340000000000004</v>
       </c>
       <c r="H196">
         <v>2200</v>
@@ -35929,7 +35929,7 @@
         <v>2.9618999999999995</v>
       </c>
       <c r="G197">
-        <v>0.34000000000000008</v>
+        <v>0.34340000000000009</v>
       </c>
       <c r="H197">
         <v>2200.0000000000005</v>
@@ -35982,7 +35982,7 @@
         <v>2.0411999999999999</v>
       </c>
       <c r="G198">
-        <v>0.34</v>
+        <v>0.34340000000000004</v>
       </c>
       <c r="H198">
         <v>2200</v>
@@ -36035,7 +36035,7 @@
         <v>0.66789999999999994</v>
       </c>
       <c r="G199">
-        <v>0.34</v>
+        <v>0.34340000000000004</v>
       </c>
       <c r="H199">
         <v>2200</v>
@@ -36088,7 +36088,7 @@
         <v>0.66789999999999994</v>
       </c>
       <c r="G200">
-        <v>0.34</v>
+        <v>0.34340000000000004</v>
       </c>
       <c r="H200">
         <v>2200</v>
@@ -36141,7 +36141,7 @@
         <v>1.4432</v>
       </c>
       <c r="G201">
-        <v>0.34000000000000008</v>
+        <v>0.34340000000000004</v>
       </c>
       <c r="H201">
         <v>2200</v>
@@ -36194,7 +36194,7 @@
         <v>1.4610999999999998</v>
       </c>
       <c r="G202">
-        <v>0.34000000000000008</v>
+        <v>0.34340000000000004</v>
       </c>
       <c r="H202">
         <v>2200</v>
@@ -36247,7 +36247,7 @@
         <v>2.6181000000000001</v>
       </c>
       <c r="G203">
-        <v>0.34000000000000008</v>
+        <v>0.34340000000000009</v>
       </c>
       <c r="H203">
         <v>2200</v>
@@ -36300,7 +36300,7 @@
         <v>0.68400000000000005</v>
       </c>
       <c r="G204">
-        <v>0.34</v>
+        <v>0.34340000000000004</v>
       </c>
       <c r="H204">
         <v>2200</v>
@@ -36353,7 +36353,7 @@
         <v>0.66789999999999994</v>
       </c>
       <c r="G205">
-        <v>0.37</v>
+        <v>0.37369999999999998</v>
       </c>
       <c r="H205">
         <v>2200</v>
@@ -36406,7 +36406,7 @@
         <v>0.59499999999999997</v>
       </c>
       <c r="G206">
-        <v>0.39500000000000002</v>
+        <v>0.39895000000000003</v>
       </c>
       <c r="H206">
         <v>2200</v>
@@ -36459,7 +36459,7 @@
         <v>1.5580999999999998</v>
       </c>
       <c r="G207">
-        <v>0.39499999999999996</v>
+        <v>0.39894999999999997</v>
       </c>
       <c r="H207">
         <v>2200</v>
@@ -36512,7 +36512,7 @@
         <v>2.3433000000000002</v>
       </c>
       <c r="G208">
-        <v>0.41499999999999992</v>
+        <v>0.41914999999999991</v>
       </c>
       <c r="H208">
         <v>2200</v>
@@ -36565,7 +36565,7 @@
         <v>1.3</v>
       </c>
       <c r="G209">
-        <v>0.34</v>
+        <v>0.34340000000000004</v>
       </c>
       <c r="H209">
         <v>2200</v>
@@ -36618,7 +36618,7 @@
         <v>1.08</v>
       </c>
       <c r="G210">
-        <v>0.34</v>
+        <v>0.34340000000000004</v>
       </c>
       <c r="H210">
         <v>2200</v>
@@ -36671,7 +36671,7 @@
         <v>1.08</v>
       </c>
       <c r="G211">
-        <v>0.34</v>
+        <v>0.34340000000000004</v>
       </c>
       <c r="H211">
         <v>2200</v>
@@ -36724,7 +36724,7 @@
         <v>0.93600000000000005</v>
       </c>
       <c r="G212">
-        <v>0.32</v>
+        <v>0.32319999999999999</v>
       </c>
       <c r="H212">
         <v>2200</v>
@@ -36777,7 +36777,7 @@
         <v>0.93600000000000005</v>
       </c>
       <c r="G213">
-        <v>0.34</v>
+        <v>0.34340000000000004</v>
       </c>
       <c r="H213">
         <v>2200</v>
@@ -36830,7 +36830,7 @@
         <v>0.92249999999999999</v>
       </c>
       <c r="G214">
-        <v>0.39499999999999996</v>
+        <v>0.39895000000000003</v>
       </c>
       <c r="H214">
         <v>2200</v>
@@ -36883,7 +36883,7 @@
         <v>1.3</v>
       </c>
       <c r="G215">
-        <v>0.34</v>
+        <v>0.34340000000000004</v>
       </c>
       <c r="H215">
         <v>2200</v>
@@ -36936,7 +36936,7 @@
         <v>1.3</v>
       </c>
       <c r="G216">
-        <v>0.34</v>
+        <v>0.34340000000000004</v>
       </c>
       <c r="H216">
         <v>2200</v>
@@ -36989,7 +36989,7 @@
         <v>0.95199999999999996</v>
       </c>
       <c r="G217">
-        <v>0.34</v>
+        <v>0.34340000000000004</v>
       </c>
       <c r="H217">
         <v>2200</v>
@@ -37042,7 +37042,7 @@
         <v>1.3</v>
       </c>
       <c r="G218">
-        <v>0.34</v>
+        <v>0.34340000000000004</v>
       </c>
       <c r="H218">
         <v>2200</v>
@@ -37095,7 +37095,7 @@
         <v>1.3</v>
       </c>
       <c r="G219">
-        <v>0.34</v>
+        <v>0.34340000000000004</v>
       </c>
       <c r="H219">
         <v>2200</v>
@@ -37148,7 +37148,7 @@
         <v>0.91400000000000003</v>
       </c>
       <c r="G220">
-        <v>0.39500000000000002</v>
+        <v>0.39895000000000003</v>
       </c>
       <c r="H220">
         <v>2200</v>
@@ -37201,7 +37201,7 @@
         <v>0.93600000000000005</v>
       </c>
       <c r="G221">
-        <v>0.32</v>
+        <v>0.32319999999999999</v>
       </c>
       <c r="H221">
         <v>2200</v>
@@ -37254,7 +37254,7 @@
         <v>0.93600000000000005</v>
       </c>
       <c r="G222">
-        <v>0.32</v>
+        <v>0.32319999999999999</v>
       </c>
       <c r="H222">
         <v>2200</v>
@@ -37307,7 +37307,7 @@
         <v>0.89300000000000002</v>
       </c>
       <c r="G223">
-        <v>0.34</v>
+        <v>0.34340000000000004</v>
       </c>
       <c r="H223">
         <v>2200</v>
@@ -37360,7 +37360,7 @@
         <v>0.8649</v>
       </c>
       <c r="G224">
-        <v>0.34</v>
+        <v>0.34340000000000004</v>
       </c>
       <c r="H224">
         <v>2200</v>
@@ -37413,7 +37413,7 @@
         <v>0.89300000000000002</v>
       </c>
       <c r="G225">
-        <v>0.34</v>
+        <v>0.34340000000000004</v>
       </c>
       <c r="H225">
         <v>2200</v>
@@ -37466,7 +37466,7 @@
         <v>1.3</v>
       </c>
       <c r="G226">
-        <v>0.34</v>
+        <v>0.34340000000000004</v>
       </c>
       <c r="H226">
         <v>2200</v>
@@ -37519,7 +37519,7 @@
         <v>0.91679999999999995</v>
       </c>
       <c r="G227">
-        <v>0.39500000000000007</v>
+        <v>0.39895000000000003</v>
       </c>
       <c r="H227">
         <v>2200</v>
@@ -37572,7 +37572,7 @@
         <v>0.87860000000000005</v>
       </c>
       <c r="G228">
-        <v>0.41499999999999998</v>
+        <v>0.41914999999999997</v>
       </c>
       <c r="H228">
         <v>2200</v>
@@ -37625,7 +37625,7 @@
         <v>0.95199999999999996</v>
       </c>
       <c r="G229">
-        <v>0.34</v>
+        <v>0.34340000000000004</v>
       </c>
       <c r="H229">
         <v>2200</v>
@@ -37678,7 +37678,7 @@
         <v>0.95199999999999996</v>
       </c>
       <c r="G230">
-        <v>0.34</v>
+        <v>0.34340000000000004</v>
       </c>
       <c r="H230">
         <v>2200</v>
@@ -37731,7 +37731,7 @@
         <v>0.88300000000000001</v>
       </c>
       <c r="G231">
-        <v>0.41499999999999998</v>
+        <v>0.41914999999999997</v>
       </c>
       <c r="H231">
         <v>2200</v>
@@ -37784,7 +37784,7 @@
         <v>0.88300000000000001</v>
       </c>
       <c r="G232">
-        <v>0.41499999999999998</v>
+        <v>0.41914999999999997</v>
       </c>
       <c r="H232">
         <v>2200</v>
@@ -37837,7 +37837,7 @@
         <v>1.3</v>
       </c>
       <c r="G233">
-        <v>0.37</v>
+        <v>0.37369999999999998</v>
       </c>
       <c r="H233">
         <v>2200</v>
@@ -37890,7 +37890,7 @@
         <v>1.3</v>
       </c>
       <c r="G234">
-        <v>0.37</v>
+        <v>0.37369999999999998</v>
       </c>
       <c r="H234">
         <v>2200</v>
@@ -37943,7 +37943,7 @@
         <v>1.008</v>
       </c>
       <c r="G235">
-        <v>0.41499999999999998</v>
+        <v>0.41914999999999997</v>
       </c>
       <c r="H235">
         <v>2200</v>
@@ -37996,7 +37996,7 @@
         <v>0.60899999999999999</v>
       </c>
       <c r="G236">
-        <v>0.43500000000000005</v>
+        <v>0.43934999999999996</v>
       </c>
       <c r="H236">
         <v>2400</v>

--- a/VerveStacks_USA/vt_vervestacks_USA_v1.xlsx
+++ b/VerveStacks_USA/vt_vervestacks_USA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_USA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B42F7927-9465-4735-BE0F-4582ACBE8B35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{772961C1-2CD5-496E-BDFB-FDB8923117B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{03B880F7-6AB4-4093-B565-A944A55A3FB1}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{5B8240BC-7C08-48E7-80A1-A5603CE7C02D}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -5507,7 +5507,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{957C2361-D968-4121-881C-2F65967D5DF7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D05A490E-093C-4D52-9254-1194A147242C}">
   <dimension ref="B9:T503"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -25986,7 +25986,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE8F245C-8A00-4630-BBDC-EF982FCC0C47}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEF98A95-93D7-4459-BDAC-53C16426C272}">
   <dimension ref="B9:T1313"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_USA/vt_vervestacks_USA_v1.xlsx
+++ b/VerveStacks_USA/vt_vervestacks_USA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_USA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{772961C1-2CD5-496E-BDFB-FDB8923117B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{59F3983A-48E5-403B-99B6-134700643D53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{5B8240BC-7C08-48E7-80A1-A5603CE7C02D}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{F2F844FC-6823-4EC0-B7AC-8E3C973327FC}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -5507,7 +5507,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D05A490E-093C-4D52-9254-1194A147242C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{860FDEE9-0DF5-4E55-BAF2-9418378E87D8}">
   <dimension ref="B9:T503"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -25986,7 +25986,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEF98A95-93D7-4459-BDAC-53C16426C272}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60D3C3BF-879A-4E5B-9E7A-BEB2E8C9A1C9}">
   <dimension ref="B9:T1313"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -70874,7 +70874,7 @@
         <v>33</v>
       </c>
       <c r="L949">
-        <v>0.24073684438920245</v>
+        <v>0.24073684438920243</v>
       </c>
     </row>
     <row r="950" spans="2:12" x14ac:dyDescent="0.45">

--- a/VerveStacks_USA/vt_vervestacks_USA_v1.xlsx
+++ b/VerveStacks_USA/vt_vervestacks_USA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_USA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{59F3983A-48E5-403B-99B6-134700643D53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{59EE26D4-7590-4A1A-802D-482138679062}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{F2F844FC-6823-4EC0-B7AC-8E3C973327FC}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{92D4A4D0-223E-4DA5-9ED6-A39675ACD01D}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -5507,7 +5507,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{860FDEE9-0DF5-4E55-BAF2-9418378E87D8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5CD74C1-1BC7-4AA3-9C59-64CE21AB22F2}">
   <dimension ref="B9:T503"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -25986,7 +25986,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60D3C3BF-879A-4E5B-9E7A-BEB2E8C9A1C9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{317CB2E0-1537-47A1-BDDF-18AB0E11248F}">
   <dimension ref="B9:T1313"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
